--- a/baseGame/ExcelData/Excel_RoleData.xlsx
+++ b/baseGame/ExcelData/Excel_RoleData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="168"/>
+    <workbookView windowWidth="30720" windowHeight="13380" tabRatio="168"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="116">
   <si>
     <t>id</t>
   </si>
@@ -48,48 +48,48 @@
     <t>is_full</t>
   </si>
   <si>
+    <t>skill_ids</t>
+  </si>
+  <si>
+    <t>prefab_path</t>
+  </si>
+  <si>
+    <t>ai_path</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>anim_path</t>
+  </si>
+  <si>
+    <t>self_buffs</t>
+  </si>
+  <si>
+    <t>move_speed</t>
+  </si>
+  <si>
+    <t>render_pos</t>
+  </si>
+  <si>
+    <t>emoji_pos</t>
+  </si>
+  <si>
+    <t>effect_pos</t>
+  </si>
+  <si>
+    <t>sky_height</t>
+  </si>
+  <si>
+    <t>ui_hp_offset</t>
+  </si>
+  <si>
+    <t>ui_hp_size</t>
+  </si>
+  <si>
     <t>attack_line</t>
   </si>
   <si>
-    <t>skill_ids</t>
-  </si>
-  <si>
-    <t>prefab_path</t>
-  </si>
-  <si>
-    <t>ai_path</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>anim_path</t>
-  </si>
-  <si>
-    <t>self_buffs</t>
-  </si>
-  <si>
-    <t>move_speed</t>
-  </si>
-  <si>
-    <t>render_pos</t>
-  </si>
-  <si>
-    <t>emoji_pos</t>
-  </si>
-  <si>
-    <t>effect_pos</t>
-  </si>
-  <si>
-    <t>sky_height</t>
-  </si>
-  <si>
-    <t>ui_hp_offset</t>
-  </si>
-  <si>
-    <t>ui_hp_size</t>
-  </si>
-  <si>
     <t>sky_size</t>
   </si>
   <si>
@@ -141,48 +141,48 @@
     <t>是完整状态</t>
   </si>
   <si>
+    <t>攻击id</t>
+  </si>
+  <si>
+    <t>预制体路径</t>
+  </si>
+  <si>
+    <t>ai路径</t>
+  </si>
+  <si>
+    <t>最大血量</t>
+  </si>
+  <si>
+    <t>动画路径</t>
+  </si>
+  <si>
+    <t>自带buff</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>预制体渲染图高度（只针对地升动画）</t>
+  </si>
+  <si>
+    <t>表情父亲位置</t>
+  </si>
+  <si>
+    <t>特效父亲位置</t>
+  </si>
+  <si>
+    <t>空中高度</t>
+  </si>
+  <si>
+    <t>ui高度</t>
+  </si>
+  <si>
+    <t>血条大小</t>
+  </si>
+  <si>
     <t>攻击长度</t>
   </si>
   <si>
-    <t>攻击id</t>
-  </si>
-  <si>
-    <t>预制体路径</t>
-  </si>
-  <si>
-    <t>ai路径</t>
-  </si>
-  <si>
-    <t>最大血量</t>
-  </si>
-  <si>
-    <t>动画路径</t>
-  </si>
-  <si>
-    <t>自带buff</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>预制体渲染图高度（只针对地升动画）</t>
-  </si>
-  <si>
-    <t>表情父亲位置</t>
-  </si>
-  <si>
-    <t>特效父亲位置</t>
-  </si>
-  <si>
-    <t>空中高度</t>
-  </si>
-  <si>
-    <t>ui高度</t>
-  </si>
-  <si>
-    <t>血条大小</t>
-  </si>
-  <si>
     <t>空中碰撞体大小</t>
   </si>
   <si>
@@ -276,12 +276,15 @@
     <t>飞龙</t>
   </si>
   <si>
-    <t>8-809</t>
+    <t>3-6</t>
   </si>
   <si>
     <t>__role/monster/dragon</t>
   </si>
   <si>
+    <t>Assets/Game/AssetDynamic/Config/AI/archer2_t1.2</t>
+  </si>
+  <si>
     <t>Assets/Game/AssetDynamic/Animations/__role/monster/dragon</t>
   </si>
   <si>
@@ -297,10 +300,13 @@
     <t>{'x':0,'y':260}</t>
   </si>
   <si>
-    <t>{'x':0,'y':2.6}</t>
-  </si>
-  <si>
-    <t>{'x':1.93,'y':2.54}</t>
+    <t>{'x':0.72,'y':0.2}</t>
+  </si>
+  <si>
+    <t>{'x':0,'y':0.8}</t>
+  </si>
+  <si>
+    <t>{'x':0.72,'y':1.6}</t>
   </si>
   <si>
     <t>龙-术士</t>
@@ -1006,7 +1012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1019,20 +1025,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1383,26 +1380,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="25.4424778761062" customWidth="1"/>
-    <col min="2" max="2" width="32.1150442477876" customWidth="1"/>
-    <col min="3" max="6" width="25.6637168141593" customWidth="1"/>
-    <col min="7" max="7" width="18.4424778761062" customWidth="1"/>
-    <col min="8" max="8" width="22.3362831858407" customWidth="1"/>
-    <col min="9" max="9" width="34.4424778761062" customWidth="1"/>
-    <col min="10" max="10" width="74.5575221238938" customWidth="1"/>
-    <col min="11" max="11" width="11.1150442477876" customWidth="1"/>
-    <col min="12" max="12" width="69.2212389380531" customWidth="1"/>
-    <col min="13" max="14" width="27" customWidth="1"/>
-    <col min="15" max="17" width="35.1150442477876" customWidth="1"/>
-    <col min="18" max="19" width="27" customWidth="1"/>
-    <col min="20" max="20" width="17.7787610619469" customWidth="1"/>
-    <col min="21" max="21" width="19.1150442477876" customWidth="1"/>
+    <col min="1" max="1" width="25.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="32.1203703703704" customWidth="1"/>
+    <col min="3" max="6" width="25.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="34.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="74.5555555555556" customWidth="1"/>
+    <col min="10" max="10" width="11.1203703703704" customWidth="1"/>
+    <col min="11" max="11" width="69.2222222222222" customWidth="1"/>
+    <col min="12" max="13" width="27" customWidth="1"/>
+    <col min="14" max="16" width="35.1203703703704" customWidth="1"/>
+    <col min="17" max="18" width="27" customWidth="1"/>
+    <col min="19" max="19" width="17.7777777777778" customWidth="1"/>
+    <col min="20" max="20" width="18.4444444444444" customWidth="1"/>
+    <col min="21" max="21" width="19.1203703703704" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
-    <col min="23" max="23" width="19.1150442477876" customWidth="1"/>
-    <col min="24" max="24" width="21.2212389380531" customWidth="1"/>
-    <col min="25" max="25" width="20.5575221238938" customWidth="1"/>
+    <col min="23" max="23" width="19.1203703703704" customWidth="1"/>
+    <col min="24" max="24" width="21.2222222222222" customWidth="1"/>
+    <col min="25" max="25" width="20.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:25">
@@ -1412,10 +1409,10 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1489,10 +1486,10 @@
       <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -1502,28 +1499,28 @@
         <v>27</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>30</v>
@@ -1532,16 +1529,16 @@
         <v>30</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>30</v>
@@ -1566,10 +1563,10 @@
       <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -1643,10 +1640,10 @@
       <c r="B4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="5" t="b">
+      <c r="C4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>1</v>
       </c>
       <c r="E4" s="4">
@@ -1655,59 +1652,59 @@
       <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="4">
+        <v>200</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4" s="4">
         <v>0.53</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="8">
-        <v>200</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="O4" s="8" t="s">
+      <c r="U4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y4" s="8" t="s">
+      <c r="Y4" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1718,8 +1715,8 @@
       <c r="B5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4">
@@ -1728,59 +1725,59 @@
       <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="4">
+        <v>200</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5" s="4">
         <v>0.53</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" s="8">
-        <v>200</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="O5" s="8" t="s">
+      <c r="U5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1791,8 +1788,8 @@
       <c r="B6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>3</v>
       </c>
       <c r="E6" s="4">
@@ -1801,59 +1798,59 @@
       <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="4">
+        <v>800</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" s="4">
         <v>0.28</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" s="8">
-        <v>800</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="8">
-        <v>2</v>
-      </c>
-      <c r="O6" s="8" t="s">
+      <c r="U6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="X6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="T6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="W6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="X6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Y6" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1864,8 +1861,8 @@
       <c r="B7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4">
@@ -1874,59 +1871,59 @@
       <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="4">
-        <v>0.28</v>
+      <c r="G7" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="8">
+        <v>84</v>
+      </c>
+      <c r="J7" s="4">
         <v>800</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="8">
+      <c r="K7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
         <v>2</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="P7" s="8" t="s">
+      <c r="N7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="O7" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="R7" s="8">
+      <c r="P7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="4">
         <v>0</v>
       </c>
-      <c r="S7" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="T7" s="8" t="s">
+      <c r="R7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="W7" s="8" t="s">
+      <c r="T7" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="X7" s="8" t="s">
+      <c r="V7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="X7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="Y7" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1941,14 +1938,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S4"/>
-  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" customFormat="1" ht="15" customHeight="1" spans="1:19">
       <c r="A1" s="1">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="b">
         <v>1</v>
@@ -1957,19 +1954,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G1" s="2">
         <v>5000</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J1" s="2">
         <v>2.5</v>
@@ -1981,25 +1978,25 @@
         <v>0</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>59</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:19">
@@ -2007,7 +2004,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="b">
         <v>0</v>
@@ -2017,16 +2014,16 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G2" s="2">
         <v>5000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J2" s="2">
         <v>10</v>
@@ -2038,25 +2035,25 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>63</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:19">
@@ -2064,7 +2061,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="b">
         <v>0</v>
@@ -2074,16 +2071,16 @@
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2">
         <v>5000</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J3" s="2">
         <v>10</v>
@@ -2095,25 +2092,25 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>63</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>59</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:19">
@@ -2121,7 +2118,7 @@
         <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2131,16 +2128,16 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G4" s="2">
         <v>5000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J4" s="2">
         <v>6</v>
@@ -2152,25 +2149,25 @@
         <v>2.19</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
